--- a/Prices list.xlsx
+++ b/Prices list.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Пользователь\Desktop\kaspi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52B99DE0-73F1-477B-AFE2-310149A82DAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6F30A69-51BB-4B16-A8F6-3FF9838CB7CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,36 +25,90 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
-  <si>
-    <t>4500 tg</t>
-  </si>
-  <si>
-    <t>67 tenge</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 86 KZT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Iphone 17 pro </t>
-  </si>
-  <si>
-    <t>yeap</t>
-  </si>
-  <si>
-    <t>1488 tenge</t>
-  </si>
-  <si>
-    <t>37 tg</t>
-  </si>
-  <si>
-    <t>67 тенге</t>
-  </si>
-  <si>
-    <t>389 тг</t>
-  </si>
-  <si>
-    <t>5000 тг</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="28">
+  <si>
+    <t>Brand</t>
+  </si>
+  <si>
+    <t>SKU (Vendor Code)</t>
+  </si>
+  <si>
+    <t>Product Name</t>
+  </si>
+  <si>
+    <t>Purchase Price (KZT)</t>
+  </si>
+  <si>
+    <t>Retail Price</t>
+  </si>
+  <si>
+    <t>Warehouse Stock (Almaty)</t>
+  </si>
+  <si>
+    <t>Warehouse Stock (Astana)</t>
+  </si>
+  <si>
+    <t>Barcode</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Samsung</t>
+  </si>
+  <si>
+    <t>SM-G991B</t>
+  </si>
+  <si>
+    <t>Смартфон Galaxy S21</t>
+  </si>
+  <si>
+    <t>320 000 Тг</t>
+  </si>
+  <si>
+    <t>Active</t>
+  </si>
+  <si>
+    <t>Apple</t>
+  </si>
+  <si>
+    <t>iPhone13-128</t>
+  </si>
+  <si>
+    <t>iPhone 13 128GB</t>
+  </si>
+  <si>
+    <t>450000KZT</t>
+  </si>
+  <si>
+    <t>OUT OF STOCK</t>
+  </si>
+  <si>
+    <t>Unknown</t>
+  </si>
+  <si>
+    <t>Hidden_Row</t>
+  </si>
+  <si>
+    <t>Old Case Model</t>
+  </si>
+  <si>
+    <t>CALL FOR PRICE</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>Archive</t>
+  </si>
+  <si>
+    <t>Xiaomi</t>
+  </si>
+  <si>
+    <t>X-MOP-2</t>
+  </si>
+  <si>
+    <t>Робот-пылесос Mi Mop 2</t>
   </si>
 </sst>
 </file>
@@ -70,11 +124,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
       <family val="2"/>
-      <scheme val="minor"/>
+      <charset val="204"/>
     </font>
   </fonts>
   <fills count="2">
@@ -85,7 +139,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -93,13 +147,36 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -380,76 +457,156 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:A14"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="14.7265625" customWidth="1"/>
-  </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A1" s="1"/>
+    <row r="1" spans="1:9" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:9" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>1</v>
+        <v>9</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" s="2">
+        <v>280000</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" s="2">
+        <v>5</v>
+      </c>
+      <c r="G2" s="2">
+        <v>0</v>
+      </c>
+      <c r="H2" s="2">
+        <v>8806090</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:9" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" s="2">
+        <v>390000</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G3" s="2">
         <v>2</v>
       </c>
+      <c r="H3" s="2">
+        <v>194252</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>13</v>
+      </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:9" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1" t="s">
-        <v>3</v>
+        <v>19</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" s="2">
+        <v>1500</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F4" s="2">
+        <v>0</v>
+      </c>
+      <c r="G4" s="2">
+        <v>0</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:9" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A6" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A7" s="1">
-        <v>6767</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A9">
         <v>25</v>
       </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
-        <v>9</v>
+      <c r="B5" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D5" s="2">
+        <v>95000</v>
+      </c>
+      <c r="E5" s="3">
+        <v>115000</v>
+      </c>
+      <c r="F5" s="2">
+        <v>12</v>
+      </c>
+      <c r="G5" s="2">
+        <v>15</v>
+      </c>
+      <c r="H5" s="2">
+        <v>6934177</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Prices list.xlsx
+++ b/Prices list.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Пользователь\Desktop\kaspi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6F30A69-51BB-4B16-A8F6-3FF9838CB7CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF37C195-24C1-4DBC-9E29-F25765F92534}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
